--- a/results/Int Task Remove ACC -0.2/Rando_5_permute.xlsx
+++ b/results/Int Task Remove ACC -0.2/Rando_5_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7620731615504972</v>
+        <v>0.7369493489404324</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.76242626889513</v>
+        <v>0.7393576801461201</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7540871254525339</v>
+        <v>0.7574295749291331</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7437115796295932</v>
+        <v>0.7498240600716197</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7471432265582549</v>
+        <v>0.7491812655890959</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7472066467649967</v>
+        <v>0.7566959463440501</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7412758345280882</v>
+        <v>0.7556366243101518</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7738214479774272</v>
+        <v>0.7559897316547846</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7669323768747831</v>
+        <v>0.7573113269307565</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7567282701913571</v>
+        <v>0.7459124653848419</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7566374360887982</v>
+        <v>0.7424808184561804</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7551975928144496</v>
+        <v>0.7431870331454459</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7389256044150283</v>
+        <v>0.7137506464769461</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7411436750004909</v>
+        <v>0.7154527629933682</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7396952393110356</v>
+        <v>0.7005948406229747</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7374411624146486</v>
+        <v>0.7092699065799897</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7376383787994841</v>
+        <v>0.7037196155835315</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.736544687105158</v>
+        <v>0.7044532441686143</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7366441136228241</v>
+        <v>0.6707177858082762</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7445204941375179</v>
+        <v>0.6597865971417536</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7218254708643479</v>
+        <v>0.6768077623059751</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7117412488297949</v>
+        <v>0.6540734594208876</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7126737304502098</v>
+        <v>0.6481270990042618</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7090706443820335</v>
+        <v>0.6475477247284797</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7090690077315369</v>
+        <v>0.6455919273850907</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7090690077315369</v>
+        <v>0.6517661913833626</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7063435754921408</v>
+        <v>0.6517661913833626</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7063435754921408</v>
+        <v>0.6218514936072432</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.705700781009617</v>
+        <v>0.626417748492645</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7074920949781016</v>
+        <v>0.6237986985355251</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7266114460789127</v>
+        <v>0.6062497135861631</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7265840321830954</v>
+        <v>0.589525191324443</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7417128202106696</v>
+        <v>0.6752611275867261</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6718004301117505</v>
+        <v>0.6486013184856401</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6178772970389719</v>
+        <v>0.6550104418301681</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6032010428736965</v>
+        <v>0.6684252476252202</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6138560467689246</v>
+        <v>0.6608180961172103</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6163912183880956</v>
+        <v>0.6377941060942318</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5968348816047031</v>
+        <v>0.648063269634896</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.632113701383297</v>
+        <v>0.6403137295336856</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6138891889414799</v>
+        <v>0.6403137295336856</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5751345326708173</v>
+        <v>0.6334127927149413</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6039780426969381</v>
+        <v>0.6334127927149413</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6039780426969381</v>
+        <v>0.6440710699111627</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5811033970317707</v>
+        <v>0.6500550732892092</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5498290518556344</v>
+        <v>0.6517657822207383</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5626865781566078</v>
+        <v>0.662083226951051</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5627090821009355</v>
+        <v>0.674421525881991</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5790584022363192</v>
+        <v>0.6422699360396986</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5726374131756912</v>
+        <v>0.6466598418340961</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5738391238027901</v>
+        <v>0.6317041295965329</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5426486569646025</v>
+        <v>0.6413084038729697</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5360202224535355</v>
+        <v>0.6242238185020066</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5561939856367553</v>
+        <v>0.5836520710175384</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5496977106532854</v>
+        <v>0.5640458163940008</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5341663066035575</v>
+        <v>0.5681116653900793</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5277760047397398</v>
+        <v>0.5678219782521882</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.533252646463853</v>
+        <v>0.566952916838515</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5432750849421608</v>
+        <v>0.5497312619884649</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5618031960510896</v>
+        <v>0.5590200718816898</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5435463597619656</v>
+        <v>0.5398749435355579</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5151230597508363</v>
+        <v>0.4866621167782862</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.527001869054867</v>
+        <v>0.4749731589318564</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.526712181916976</v>
+        <v>0.5158546425227986</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4898196247487742</v>
+        <v>0.5024742063881742</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.506160352469051</v>
+        <v>0.5122617855202257</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.506160352469051</v>
+        <v>0.5308103547603616</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5074647629148091</v>
+        <v>0.5308103547603616</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5094651589842292</v>
+        <v>0.5372194781048897</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5094651589842292</v>
+        <v>0.6044682195206578</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5171529155291946</v>
+        <v>0.5910673252548264</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5112204666417896</v>
+        <v>0.5912301719792342</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5052434190283533</v>
+        <v>0.5313074873486916</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5032790292698575</v>
+        <v>0.5213656539073394</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5044291854063149</v>
+        <v>0.5253852675268902</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5010969649953192</v>
+        <v>0.5274613586817762</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5045372043390878</v>
+        <v>0.5103902756774097</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5018117720996916</v>
+        <v>0.5144835385693056</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5013318243415755</v>
+        <v>0.5138407440867817</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5022917198578079</v>
+        <v>0.489173147802633</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5032242014782228</v>
+        <v>0.4500649750247134</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5031967875824054</v>
+        <v>0.4489336403689665</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5020740453417654</v>
+        <v>0.4311461136097309</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4997651406537437</v>
+        <v>0.4840835739209564</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5025265792040641</v>
+        <v>0.5296892491702182</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5025265792040641</v>
+        <v>0.5064136241333935</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5034230545135547</v>
+        <v>0.5014529364783209</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5025454006847746</v>
+        <v>0.5085273582497005</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5019488415787785</v>
+        <v>0.5049860557377693</v>
       </c>
     </row>
   </sheetData>
